--- a/artfynd/A 49941-2025 artfynd.xlsx
+++ b/artfynd/A 49941-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>725045</v>
       </c>
       <c r="B2" t="n">
-        <v>93053</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>470499.3835917815</v>
+        <v>470499</v>
       </c>
       <c r="R2" t="n">
-        <v>6246389.250541092</v>
+        <v>6246389</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2009-09-16</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2009-09-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -800,12 +785,7 @@
         <v>6221953</v>
       </c>
       <c r="B3" t="n">
-        <v>95520</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97985</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -833,10 +813,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>470499.3835917815</v>
+        <v>470499</v>
       </c>
       <c r="R3" t="n">
-        <v>6246389.250541092</v>
+        <v>6246389</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -866,19 +846,9 @@
           <t>2009-09-16</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2009-09-16</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
